--- a/data/trans_orig/P70D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023</t>
+          <t>Población con capacidad laboral &lt;=6 (Likert 0 a 10) en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6924</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>19929</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28953</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18498</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45748</t>
+          <t>45405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111856</t>
+          <t>110855</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>123860</t>
+          <t>124335</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>49613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>70227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164818</t>
+          <t>165161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>192068</t>
+          <t>191429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,91%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24774</t>
+          <t>26182</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65145</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61408</t>
+          <t>61122</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64323</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116580</t>
+          <t>119101</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1316539</t>
+          <t>1317421</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1356910</t>
+          <t>1355502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>883997</t>
+          <t>884283</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>911518</t>
+          <t>911545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2210509</t>
+          <t>2207988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2262766</t>
+          <t>2263562</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9453</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30234</t>
+          <t>30034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53209</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420360</t>
+          <t>420560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>441141</t>
+          <t>440387</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>407183</t>
+          <t>409298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424297</t>
+          <t>424072</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835676</t>
+          <t>835490</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>861527</t>
+          <t>860638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50563</t>
+          <t>49866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>98960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65734</t>
+          <t>65424</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>107325</t>
+          <t>106449</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122967</t>
+          <t>123810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193078</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1864622</t>
+          <t>1864102</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1912499</t>
+          <t>1913196</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1356152</t>
+          <t>1357028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1397743</t>
+          <t>1398053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3233462</t>
+          <t>3237343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3303573</t>
+          <t>3302730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P70D_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19929</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16154</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27688</t>
+          <t>27993</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19137</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119250</t>
+          <t>148332</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110855</t>
+          <t>139683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>124335</t>
+          <t>154475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>63628</t>
+          <t>73141</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49613</t>
+          <t>66601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70227</t>
+          <t>78340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>182878</t>
+          <t>221473</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165161</t>
+          <t>211496</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>191429</t>
+          <t>230118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>92,24%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>130784</t>
+          <t>162433</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>87033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>210566</t>
+          <t>249466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47585</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26182</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64263</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>53473</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33860</t>
+          <t>41940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61122</t>
+          <t>67642</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>94160</t>
+          <t>103693</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63527</t>
+          <t>85225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119101</t>
+          <t>126158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1334099</t>
+          <t>1221080</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1317421</t>
+          <t>1205749</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1355502</t>
+          <t>1233355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>898830</t>
+          <t>892330</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>884283</t>
+          <t>878161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>911545</t>
+          <t>903863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2232929</t>
+          <t>2113410</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2207988</t>
+          <t>2090945</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2263562</t>
+          <t>2131878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1381684</t>
+          <t>1271300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1381684</t>
+          <t>1271300</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1381684</t>
+          <t>1271300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>945405</t>
+          <t>945803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>945405</t>
+          <t>945803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>945405</t>
+          <t>945803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2327089</t>
+          <t>2217103</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2327089</t>
+          <t>2217103</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2327089</t>
+          <t>2217103</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30034</t>
+          <t>32327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21051</t>
+          <t>22355</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28992</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>38836</t>
+          <t>41073</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28247</t>
+          <t>29960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53395</t>
+          <t>57576</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>432809</t>
+          <t>472929</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420560</t>
+          <t>459320</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440387</t>
+          <t>481813</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>458951</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>409298</t>
+          <t>448917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>424072</t>
+          <t>465778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>850049</t>
+          <t>931880</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>835490</t>
+          <t>915377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860638</t>
+          <t>942993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>450594</t>
+          <t>491647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>438290</t>
+          <t>481306</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>438290</t>
+          <t>481306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>438290</t>
+          <t>481306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>888885</t>
+          <t>972953</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>888885</t>
+          <t>972953</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>888885</t>
+          <t>972953</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76904</t>
+          <t>83039</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>49866</t>
+          <t>65108</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98960</t>
+          <t>101650</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>83780</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65424</t>
+          <t>75024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>106449</t>
+          <t>107392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>160684</t>
+          <t>172759</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123810</t>
+          <t>146873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>195659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1886158</t>
+          <t>1842341</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1864102</t>
+          <t>1823730</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1913196</t>
+          <t>1860272</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1379697</t>
+          <t>1424422</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1357028</t>
+          <t>1406750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1398053</t>
+          <t>1439118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3265856</t>
+          <t>3266763</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3237343</t>
+          <t>3243863</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3302730</t>
+          <t>3292649</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1963062</t>
+          <t>1925380</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1963062</t>
+          <t>1925380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1963062</t>
+          <t>1925380</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1463477</t>
+          <t>1514142</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1463477</t>
+          <t>1514142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1463477</t>
+          <t>1514142</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3426540</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3426540</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3426540</t>
+          <t>3439522</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
